--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.84" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.84" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.84.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.84.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0084.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0084.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.84" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.84" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,22 +422,22 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -603,18 +603,18 @@
           <t>L16: suspicious token(s): other0 (letter/digit mix) | candidate OCR token mismatch vs other OCR: "other" vs "other0" :: said, by reason of his being concealed, or for some other0</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: served with subpo Ã¦ na out of the jurisdiction, or that the</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: is to be set down toâ€™ be heard ; and the Court, if it so, made,</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 77</t>
@@ -622,13 +622,17 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • by himself or his own solicitor, or upon notice served up-</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -666,14 +670,10 @@
           <t>L19: suspicious token(s): being2 (letter/digit mix) | candidate OCR token mismatch vs other OCR: "being" vs "being2" :: Gazette as herein provided. And the Court, being2</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ã€� 4</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ by himself or his own solicitor, or upon notice served up-</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • by himself or his own solicitor, or upon notice served up-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -732,7 +732,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 550.â€�</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L61: symbol-only separator/garbage line :: 550.”</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -766,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -789,11 +789,7 @@
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -801,7 +797,11 @@
           <t>L19: symbol-only separator/garbage line :: 880.</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -970,7 +970,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: e</t>
+          <t>L58: isolated marker/symbol line :: 、 4</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: '</t>
+          <t>L65: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 1</t>
+          <t>L81: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L107: symbol-only separator/garbage line :: 880.</t>
+          <t>L95: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: '</t>
+          <t>L107: symbol-only separator/garbage line :: 880.</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L136: isolated marker/symbol line :: X</t>
+          <t>L126: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr"/>
@@ -1226,7 +1226,11 @@
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="1" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>L136: isolated marker/symbol line :: X</t>
+        </is>
+      </c>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
